--- a/YRIGOYEN 9730/Noviembre/YRIGOYEN7630-Noviembre.xlsx
+++ b/YRIGOYEN 9730/Noviembre/YRIGOYEN7630-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9730\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EC6701-4550-4046-9A80-1ABA31030E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED074BA7-BB7B-4106-9B5D-4D47FE0C3D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -332,9 +332,6 @@
     <t>Ascensores lema - Mantenimiento agosto</t>
   </si>
   <si>
-    <t>Transf 11/09</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fumigacion </t>
   </si>
   <si>
@@ -347,18 +344,6 @@
     <t>Transf 14/10</t>
   </si>
   <si>
-    <t>VTO 14/11</t>
-  </si>
-  <si>
-    <t>PERÍODO: OCTUBRE</t>
-  </si>
-  <si>
-    <t>Gustavo padron - Sr contador honorarios OCTUBRE</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de OCTUBRE</t>
-  </si>
-  <si>
     <t>Debito 02/10</t>
   </si>
   <si>
@@ -386,7 +371,25 @@
     <t>Debito 29/10</t>
   </si>
   <si>
-    <t>Transf 29/10</t>
+    <t>VTO 15/12</t>
+  </si>
+  <si>
+    <t>PERÍODO: NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Destapaciones italoamericana - Mantenimiento de cañertias, repaso a camaras de cloacas, ramales, salida a colectora. Mayo junio julio agosto septiembre</t>
+  </si>
+  <si>
+    <t>Transf 18/11</t>
+  </si>
+  <si>
+    <t>Transf 11/11</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1107,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1367,35 +1370,72 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1403,46 +1443,11 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1808,22 +1813,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M128"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>58</v>
@@ -1832,7 +1837,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>28</v>
@@ -1841,16 +1846,16 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="192" t="s">
+      <c r="B3" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="193"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="190"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1861,12 +1866,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1874,7 +1879,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>59</v>
       </c>
@@ -1885,57 +1890,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="195" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="195"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="194" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="194" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="194"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="194"/>
+      <c r="C9" s="194"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="193" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
-      <c r="B16" s="194"/>
-      <c r="C16" s="194"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="194"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1944,7 +1949,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>35</v>
       </c>
@@ -1953,7 +1958,7 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>79</v>
       </c>
@@ -1964,14 +1969,14 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="160"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
@@ -1984,7 +1989,7 @@
       <c r="E24" s="144"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>47</v>
       </c>
@@ -1993,28 +1998,28 @@
       <c r="D25" s="160"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="160"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="160"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="170"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
@@ -2023,7 +2028,7 @@
       <c r="D29" s="170"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
@@ -2032,7 +2037,7 @@
       <c r="D30" s="170"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
@@ -2043,14 +2048,14 @@
       </c>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="170"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="59" t="s">
         <v>36</v>
       </c>
@@ -2062,7 +2067,7 @@
       </c>
       <c r="E33" s="144"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="30" t="s">
         <v>1</v>
       </c>
@@ -2075,7 +2080,7 @@
       </c>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="36" t="s">
         <v>19</v>
       </c>
@@ -2084,22 +2089,22 @@
       <c r="D35" s="173"/>
       <c r="E35" s="146"/>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="190" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" s="191"/>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="187" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="188"/>
       <c r="C36" s="54"/>
       <c r="D36" s="160">
         <v>35000</v>
       </c>
       <c r="E36" s="147"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="190" t="s">
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="187" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="191"/>
+      <c r="B37" s="188"/>
       <c r="C37" s="54"/>
       <c r="D37" s="174">
         <v>112400</v>
@@ -2109,7 +2114,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="30" t="s">
         <v>16</v>
       </c>
@@ -2121,7 +2126,7 @@
         <v>147400</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="36" t="s">
         <v>32</v>
       </c>
@@ -2130,22 +2135,22 @@
       <c r="D39" s="176"/>
       <c r="E39" s="149"/>
     </row>
-    <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="188" t="s">
+    <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="191" t="s">
         <v>98</v>
       </c>
-      <c r="B40" s="189"/>
+      <c r="B40" s="192"/>
       <c r="C40" s="56"/>
       <c r="D40" s="177">
         <v>26570</v>
       </c>
       <c r="E40" s="161" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="166" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B41" s="159"/>
       <c r="C41" s="56"/>
@@ -2153,14 +2158,14 @@
         <v>6152</v>
       </c>
       <c r="E41" s="161" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="188" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="191" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="189"/>
+      <c r="B42" s="192"/>
       <c r="C42" s="56"/>
       <c r="D42" s="178">
         <v>54278</v>
@@ -2170,7 +2175,7 @@
         <v>Debito 02/10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="30" t="s">
         <v>2</v>
       </c>
@@ -2182,7 +2187,7 @@
         <v>87000</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="36" t="s">
         <v>17</v>
       </c>
@@ -2191,54 +2196,54 @@
       <c r="D44" s="179"/>
       <c r="E44" s="153"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="54"/>
-      <c r="D45" s="211">
-        <v>544619.34</v>
+      <c r="D45" s="213">
+        <v>553442.28</v>
       </c>
       <c r="E45" s="161" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G45" s="127"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="54"/>
-      <c r="D46" s="211">
+      <c r="D46" s="186">
         <v>119008</v>
       </c>
       <c r="E46" s="161" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G46" s="127"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="54"/>
-      <c r="D47" s="211">
+      <c r="D47" s="186">
         <v>10602.27</v>
       </c>
       <c r="E47" s="161" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="211">
+      <c r="D48" s="186">
         <v>75532.289999999994</v>
       </c>
       <c r="E48" s="161" t="str">
@@ -2247,50 +2252,50 @@
       </c>
       <c r="G48" s="143"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="164">
-        <v>77379.429999999993</v>
+      <c r="D49" s="212">
+        <v>78639.69</v>
       </c>
       <c r="E49" s="161" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="str">
         <f>A49</f>
-        <v>Sindicatos mes de OCTUBRE</v>
+        <v>Sindicatos mes de NOVIEMBRE</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="164">
-        <v>4974.57</v>
+      <c r="D50" s="212">
+        <v>5054.8999999999996</v>
       </c>
       <c r="E50" s="162" t="str">
         <f>E49</f>
         <v>Debito 13/10</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de OCTUBRE</v>
+        <v>Sindicatos mes de NOVIEMBRE</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="164">
-        <v>44771.13</v>
+      <c r="D51" s="212">
+        <v>45494.1</v>
       </c>
       <c r="E51" s="163" t="str">
         <f>E50</f>
         <v>Debito 13/10</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="30" t="s">
         <v>3</v>
       </c>
@@ -2299,10 +2304,10 @@
       <c r="D52" s="180"/>
       <c r="E52" s="151">
         <f>SUM(D45:D51)</f>
-        <v>876887.03</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>887773.53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="36" t="s">
         <v>18</v>
       </c>
@@ -2311,59 +2316,59 @@
       <c r="D53" s="179"/>
       <c r="E53" s="153"/>
     </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="164">
-        <v>54234.99</v>
+      <c r="D54" s="212">
+        <v>51958.1</v>
       </c>
       <c r="E54" s="161" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B55" s="164"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="164">
-        <v>27593.64</v>
+      <c r="D55" s="212">
+        <v>11573.69</v>
       </c>
       <c r="E55" s="185" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="164">
-        <v>26441.68</v>
+      <c r="D56" s="212">
+        <v>26736.26</v>
       </c>
       <c r="E56" s="161" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="188" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="191" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="189"/>
+      <c r="B57" s="192"/>
       <c r="C57" s="5"/>
       <c r="D57" s="164">
         <v>426357.06</v>
       </c>
       <c r="E57" s="165" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="s">
         <v>4</v>
       </c>
@@ -2372,542 +2377,554 @@
       <c r="D58" s="181"/>
       <c r="E58" s="151">
         <f>SUM(D54:D57)</f>
-        <v>534627.37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>516625.11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="36"/>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
       <c r="D59" s="175"/>
       <c r="E59" s="154"/>
     </row>
-    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="166" t="s">
         <v>100</v>
       </c>
       <c r="B60" s="159"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="164">
-        <v>77500</v>
+      <c r="D60" s="212">
+        <v>81700</v>
       </c>
       <c r="E60" s="165" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="166" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B61" s="159"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="164">
-        <v>61350</v>
+      <c r="D61" s="212">
+        <v>67450</v>
       </c>
       <c r="E61" s="165" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="188" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="189"/>
+    <row r="62" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="192"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="109">
-        <v>0</v>
-      </c>
-      <c r="E62" s="165" t="s">
+      <c r="D62" s="131">
+        <v>325000</v>
+      </c>
+      <c r="E62" s="165"/>
+    </row>
+    <row r="63" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="191" t="s">
         <v>101</v>
       </c>
-      <c r="I62" s="188"/>
-      <c r="J62" s="189"/>
-    </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="30" t="s">
+      <c r="B63" s="192"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="131">
+        <v>45000</v>
+      </c>
+      <c r="E63" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="I63" s="191"/>
+      <c r="J63" s="192"/>
+    </row>
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="155">
-        <f>SUM(D60:D62)</f>
-        <v>138850</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="36" t="s">
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="155">
+        <f>SUM(D60:D63)</f>
+        <v>519150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="69"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="172"/>
-      <c r="E64" s="154"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+      <c r="B65" s="69"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="172"/>
+      <c r="E65" s="154"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="164">
-        <v>53000</v>
-      </c>
-      <c r="E65" s="156"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="164">
+        <v>53000</v>
+      </c>
+      <c r="E66" s="156"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="164">
         <v>62873.69</v>
       </c>
-      <c r="E66" s="41"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="53" t="s">
+      <c r="E67" s="41"/>
+    </row>
+    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B67" s="53"/>
-      <c r="C67" s="53"/>
-      <c r="D67" s="112"/>
-      <c r="E67" s="106">
-        <f>SUM(D65:D66)</f>
+      <c r="B68" s="53"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="112"/>
+      <c r="E68" s="106">
+        <f>SUM(D66:D67)</f>
         <v>115873.69</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="105"/>
-      <c r="E68" s="113"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="31" t="s">
+    <row r="69" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="105"/>
+      <c r="E69" s="113"/>
+    </row>
+    <row r="70" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="114"/>
-      <c r="E69" s="115">
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="114"/>
+      <c r="E70" s="115">
         <f>3774269.17-2661401.09</f>
         <v>1112868.08</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
-      <c r="D70" s="116"/>
-      <c r="E70" s="117"/>
-      <c r="F70" s="45"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="1"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="117"/>
+      <c r="F71" s="45"/>
+    </row>
+    <row r="72" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="119">
-        <f>(SUM(E27:E69))</f>
-        <v>3774269.17</v>
-      </c>
-      <c r="F71" s="143"/>
-      <c r="G71" s="45"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="116"/>
-      <c r="E72" s="116"/>
-    </row>
-    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="10"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="118"/>
+      <c r="E72" s="119">
+        <f>(SUM(E27:E70))</f>
+        <v>4147453.41</v>
+      </c>
+      <c r="F72" s="143"/>
+      <c r="G72" s="45"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D73" s="116"/>
       <c r="E73" s="116"/>
-      <c r="H73" s="182"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+    </row>
+    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D74" s="116"/>
+      <c r="E74" s="116"/>
+      <c r="H74" s="182"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="120"/>
-      <c r="E74" s="121"/>
-    </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="188"/>
-      <c r="B75" s="189"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="131"/>
-      <c r="E75" s="107"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="188"/>
-      <c r="B76" s="189"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="120"/>
+      <c r="E75" s="121"/>
+    </row>
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="191"/>
+      <c r="B76" s="192"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="109"/>
+      <c r="D76" s="131"/>
       <c r="E76" s="107"/>
     </row>
-    <row r="77" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="190"/>
-      <c r="B77" s="191"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="191"/>
+      <c r="B77" s="192"/>
       <c r="C77" s="5"/>
       <c r="D77" s="109"/>
       <c r="E77" s="107"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="108"/>
-      <c r="B78" s="110"/>
+    <row r="78" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="187"/>
+      <c r="B78" s="188"/>
       <c r="C78" s="5"/>
       <c r="D78" s="109"/>
       <c r="E78" s="107"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="51"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60">
-        <f>SUM(D75:D78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="31" t="s">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="108"/>
+      <c r="B79" s="110"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="109"/>
+      <c r="E79" s="107"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="51"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60">
+        <f>SUM(D76:D79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="31"/>
-      <c r="C82" s="31"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="104"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="104"/>
+    </row>
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="10"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="70">
-        <f>E79+E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="102" t="s">
+      <c r="B85" s="10"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="70">
+        <f>E80+E83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="B86" s="103">
-        <f>E71</f>
-        <v>3774269.17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="102" t="s">
+      <c r="B87" s="103">
+        <f>E72</f>
+        <v>4147453.41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="103">
-        <f>E71-E69</f>
-        <v>2661401.09</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="102" t="s">
+      <c r="B88" s="103">
+        <f>E72-E70</f>
+        <v>3034585.33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="B88" s="103">
-        <f>E84-E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="102" t="s">
+      <c r="B89" s="103">
+        <f>E85-E83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="103">
-        <f>E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="186"/>
-      <c r="B92" s="186"/>
-      <c r="C92" s="186"/>
-      <c r="D92" s="186"/>
-      <c r="E92" s="186"/>
-    </row>
-    <row r="93" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="186"/>
-      <c r="B93" s="186"/>
-      <c r="C93" s="186"/>
-      <c r="D93" s="186"/>
-      <c r="E93" s="186"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="186"/>
-      <c r="B94" s="186"/>
-      <c r="C94" s="186"/>
-      <c r="D94" s="186"/>
-      <c r="E94" s="186"/>
-    </row>
-    <row r="96" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="23" t="s">
+      <c r="B90" s="103">
+        <f>E85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="195"/>
+      <c r="B93" s="195"/>
+      <c r="C93" s="195"/>
+      <c r="D93" s="195"/>
+      <c r="E93" s="195"/>
+    </row>
+    <row r="94" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="195"/>
+      <c r="B94" s="195"/>
+      <c r="C94" s="195"/>
+      <c r="D94" s="195"/>
+      <c r="E94" s="195"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="195"/>
+      <c r="B95" s="195"/>
+      <c r="C95" s="195"/>
+      <c r="D95" s="195"/>
+      <c r="E95" s="195"/>
+    </row>
+    <row r="97" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B96" s="128"/>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="34"/>
-      <c r="B97" s="61">
-        <v>0</v>
-      </c>
-      <c r="C97" s="26"/>
-    </row>
-    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+      <c r="B97" s="128"/>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="34"/>
+      <c r="B98" s="61">
+        <v>0</v>
+      </c>
+      <c r="C98" s="26"/>
+    </row>
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B98" s="41">
+      <c r="B99" s="41">
         <f>PRORRATEO!F29</f>
         <v>3982800.4400000004</v>
       </c>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="25"/>
-      <c r="B99" s="41">
-        <v>0</v>
-      </c>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="25" t="s">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="25"/>
+      <c r="B100" s="41">
+        <v>0</v>
+      </c>
+      <c r="C100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B100" s="111">
-        <f>B122</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="24"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="28"/>
-      <c r="B101" s="49"/>
+      <c r="B101" s="111">
+        <f>B123</f>
+        <v>0</v>
+      </c>
       <c r="C101" s="24"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="126" t="s">
-        <v>49</v>
-      </c>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="28"/>
       <c r="B102" s="49"/>
       <c r="C102" s="24"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="40" t="s">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="126" t="s">
+        <v>49</v>
+      </c>
+      <c r="B103" s="49"/>
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B103" s="49">
-        <f>-B87</f>
-        <v>-2661401.09</v>
-      </c>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="28" t="s">
+      <c r="B104" s="49">
+        <f>-B88</f>
+        <v>-3034585.33</v>
+      </c>
+      <c r="C104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B104" s="49">
-        <f>-(B88)</f>
-        <v>0</v>
-      </c>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="33" t="s">
+      <c r="B105" s="49">
+        <f>-(B89)</f>
+        <v>0</v>
+      </c>
+      <c r="C105" s="24"/>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="61">
-        <f>SUM(B97:B104)</f>
-        <v>1321399.3500000006</v>
-      </c>
-      <c r="C105" s="27"/>
-      <c r="D105" s="45"/>
-    </row>
-    <row r="106" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="42"/>
+      <c r="B106" s="61">
+        <f>SUM(B98:B105)</f>
+        <v>948215.11000000034</v>
+      </c>
       <c r="C106" s="27"/>
       <c r="D106" s="45"/>
-      <c r="E106" s="129"/>
-      <c r="F106" s="130"/>
-    </row>
-    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="43"/>
+    </row>
+    <row r="107" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="42"/>
       <c r="C107" s="27"/>
-    </row>
-    <row r="108" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108" s="42"/>
-      <c r="C108" s="38"/>
-    </row>
-    <row r="109" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="134" t="s">
+      <c r="D107" s="45"/>
+      <c r="E107" s="129"/>
+      <c r="F107" s="130"/>
+    </row>
+    <row r="108" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="43"/>
+      <c r="C108" s="27"/>
+    </row>
+    <row r="109" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109"/>
+      <c r="B109" s="42"/>
+      <c r="C109" s="38"/>
+    </row>
+    <row r="110" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="134" t="s">
         <v>91</v>
       </c>
-      <c r="B109" s="135">
+      <c r="B110" s="135">
         <v>-1100839.9560999968</v>
       </c>
-      <c r="C109" s="38"/>
-      <c r="D109" s="48"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="56" t="s">
+      <c r="C110" s="38"/>
+      <c r="D110" s="48"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="56" t="s">
         <v>54</v>
-      </c>
-      <c r="B110" s="140">
-        <f>-B87</f>
-        <v>-2661401.09</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="56" t="s">
-        <v>55</v>
       </c>
       <c r="B111" s="140">
         <f>-B88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-3034585.33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B112" s="140">
+        <f>-B89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="B112" s="140">
-        <f>B122</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="56" t="s">
+      <c r="B113" s="140">
+        <f>B123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B113" s="141">
+      <c r="B114" s="141">
         <f>PRORRATEO!F29</f>
         <v>3982800.4400000004</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="142" t="s">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="B114" s="183"/>
-    </row>
-    <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="138" t="s">
+      <c r="B115" s="183"/>
+    </row>
+    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B115" s="139">
-        <f>SUM(B109:C114)</f>
-        <v>220559.39390000375</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="136"/>
-      <c r="B116" s="136"/>
-    </row>
-    <row r="117" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="187" t="s">
+      <c r="B116" s="139">
+        <f>SUM(B110:C115)</f>
+        <v>-152624.84609999647</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="136"/>
+      <c r="B117" s="136"/>
+    </row>
+    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="196" t="s">
         <v>33</v>
       </c>
-      <c r="B118" s="187"/>
-      <c r="C118" s="187"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="187"/>
-      <c r="B119" s="187"/>
-      <c r="C119" s="187"/>
-    </row>
-    <row r="120" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="123"/>
-      <c r="B120" s="37"/>
-      <c r="C120" s="37">
+      <c r="B119" s="196"/>
+      <c r="C119" s="196"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="196"/>
+      <c r="B120" s="196"/>
+      <c r="C120" s="196"/>
+    </row>
+    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="123"/>
+      <c r="B121" s="37"/>
+      <c r="C121" s="37">
         <v>40000</v>
       </c>
-      <c r="E120" s="143"/>
-    </row>
-    <row r="121" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="123"/>
-      <c r="B121" s="125"/>
-      <c r="C121" s="122"/>
-      <c r="D121" s="143"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="46" t="s">
+      <c r="E121" s="143"/>
+    </row>
+    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="123"/>
+      <c r="B122" s="125"/>
+      <c r="C122" s="122"/>
+      <c r="D122" s="143"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B122" s="124">
-        <f>SUM(B120:B121)</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="47"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M123" s="8"/>
-    </row>
-    <row r="124" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="186"/>
-      <c r="B124" s="186"/>
-      <c r="C124" s="186"/>
-      <c r="D124" s="186"/>
-      <c r="E124" s="186"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="186"/>
-      <c r="B125" s="186"/>
-      <c r="C125" s="186"/>
-      <c r="D125" s="186"/>
-      <c r="E125" s="186"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="186"/>
-      <c r="B126" s="186"/>
-      <c r="C126" s="186"/>
-      <c r="D126" s="186"/>
-      <c r="E126" s="186"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="186"/>
-      <c r="B127" s="186"/>
-      <c r="C127" s="186"/>
-      <c r="D127" s="186"/>
-      <c r="E127" s="186"/>
+      <c r="B123" s="124">
+        <f>SUM(B121:B122)</f>
+        <v>0</v>
+      </c>
+      <c r="C123" s="47"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M124" s="8"/>
+    </row>
+    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="195"/>
+      <c r="B125" s="195"/>
+      <c r="C125" s="195"/>
+      <c r="D125" s="195"/>
+      <c r="E125" s="195"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="195"/>
+      <c r="B126" s="195"/>
+      <c r="C126" s="195"/>
+      <c r="D126" s="195"/>
+      <c r="E126" s="195"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="195"/>
+      <c r="B127" s="195"/>
+      <c r="C127" s="195"/>
+      <c r="D127" s="195"/>
+      <c r="E127" s="195"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="195"/>
+      <c r="B128" s="195"/>
+      <c r="C128" s="195"/>
+      <c r="D128" s="195"/>
+      <c r="E128" s="195"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A125:E128"/>
+    <mergeCell ref="A119:C120"/>
+    <mergeCell ref="A93:E95"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A78:B78"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A124:E127"/>
-    <mergeCell ref="A118:C119"/>
-    <mergeCell ref="A92:E94"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A62:B62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2918,44 +2935,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="0.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0.109375" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2980,7 +2997,7 @@
       <c r="N2" s="57"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2996,71 +3013,71 @@
       <c r="M3" s="58"/>
       <c r="N3" s="62"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="198" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="198" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="198" t="s">
+      <c r="F4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="206" t="s">
+      <c r="G4" s="204" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="202" t="s">
+      <c r="H4" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="202" t="s">
+      <c r="I4" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="202" t="s">
+      <c r="J4" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="209" t="s">
+      <c r="K4" s="207" t="s">
         <v>86</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="204" t="s">
+      <c r="M4" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="196" t="s">
+      <c r="N4" s="209" t="s">
         <v>38</v>
       </c>
       <c r="Q4" s="45"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="200"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="200"/>
-      <c r="G5" s="207"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="210"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="203"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="208"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/11</v>
-      </c>
-      <c r="M5" s="205"/>
-      <c r="N5" s="197"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/12</v>
+      </c>
+      <c r="M5" s="201"/>
+      <c r="N5" s="210"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3113,7 +3130,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3166,7 +3183,7 @@
       </c>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3220,7 +3237,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3276,7 +3293,7 @@
       </c>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3332,7 +3349,7 @@
       </c>
       <c r="Q10" s="45"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3387,7 +3404,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3442,7 +3459,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3500,7 +3517,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3555,7 +3572,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3610,7 +3627,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3665,7 +3682,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3720,7 +3737,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3775,7 +3792,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3829,7 +3846,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3884,7 +3901,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -3940,7 +3957,7 @@
       </c>
       <c r="Q21" s="44"/>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -3995,7 +4012,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4050,7 +4067,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
@@ -4070,7 +4087,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="86"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4087,7 +4104,7 @@
       <c r="N25" s="85"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="86"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4104,7 +4121,7 @@
       <c r="N26" s="85"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="87"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4121,7 +4138,7 @@
       <c r="N27" s="85"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="66"/>
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
@@ -4138,7 +4155,7 @@
       <c r="N28" s="96"/>
       <c r="O28" s="45"/>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="97"/>
       <c r="B29" s="98"/>
       <c r="C29" s="98"/>
@@ -4187,94 +4204,100 @@
         <v>4969552.71</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="186" t="str">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="195" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="186"/>
-      <c r="D32" s="186"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="186"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="186"/>
-      <c r="K32" s="186"/>
-      <c r="L32" s="186"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="186"/>
-      <c r="C33" s="186"/>
-      <c r="D33" s="186"/>
-      <c r="E33" s="186"/>
-      <c r="F33" s="186"/>
-      <c r="G33" s="186"/>
-      <c r="H33" s="186"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="186"/>
-      <c r="K33" s="186"/>
-      <c r="L33" s="186"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="186"/>
-      <c r="C34" s="186"/>
-      <c r="D34" s="186"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="186"/>
-      <c r="I34" s="186"/>
-      <c r="J34" s="186"/>
-      <c r="K34" s="186"/>
-      <c r="L34" s="186"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="186"/>
-      <c r="C35" s="186"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="186"/>
-      <c r="H35" s="186"/>
-      <c r="I35" s="186"/>
-      <c r="J35" s="186"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="186"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="186"/>
-      <c r="C36" s="186"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="186"/>
-      <c r="G36" s="186"/>
-      <c r="H36" s="186"/>
-      <c r="I36" s="186"/>
-      <c r="J36" s="186"/>
-      <c r="K36" s="186"/>
-      <c r="L36" s="186"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="186"/>
-      <c r="C37" s="186"/>
-      <c r="D37" s="186"/>
-      <c r="E37" s="186"/>
-      <c r="F37" s="186"/>
-      <c r="G37" s="186"/>
-      <c r="H37" s="186"/>
-      <c r="I37" s="186"/>
-      <c r="J37" s="186"/>
-      <c r="K37" s="186"/>
-      <c r="L37" s="186"/>
+      <c r="C32" s="195"/>
+      <c r="D32" s="195"/>
+      <c r="E32" s="195"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="195"/>
+      <c r="H32" s="195"/>
+      <c r="I32" s="195"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="195"/>
+      <c r="L32" s="195"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="195"/>
+      <c r="C33" s="195"/>
+      <c r="D33" s="195"/>
+      <c r="E33" s="195"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="195"/>
+      <c r="H33" s="195"/>
+      <c r="I33" s="195"/>
+      <c r="J33" s="195"/>
+      <c r="K33" s="195"/>
+      <c r="L33" s="195"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="195"/>
+      <c r="C34" s="195"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="195"/>
+      <c r="H34" s="195"/>
+      <c r="I34" s="195"/>
+      <c r="J34" s="195"/>
+      <c r="K34" s="195"/>
+      <c r="L34" s="195"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="195"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="195"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="195"/>
+      <c r="H35" s="195"/>
+      <c r="I35" s="195"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="195"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="195"/>
+      <c r="C36" s="195"/>
+      <c r="D36" s="195"/>
+      <c r="E36" s="195"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="195"/>
+      <c r="H36" s="195"/>
+      <c r="I36" s="195"/>
+      <c r="J36" s="195"/>
+      <c r="K36" s="195"/>
+      <c r="L36" s="195"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="195"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="195"/>
+      <c r="E37" s="195"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="195"/>
+      <c r="I37" s="195"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="195"/>
+      <c r="L37" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4284,12 +4307,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4299,9 +4316,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C5" s="184" t="s">
         <v>92</v>
       </c>
